--- a/JsonConverter/JsonConverter/ExcelFiles/Default.xlsx
+++ b/JsonConverter/JsonConverter/ExcelFiles/Default.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Oz6_07_RPG\Oz6-TeamPortfolio3D_RPG\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Oz6_07_RPG\Oz6-TeamPortfolio3D_RPG\JsonConverter\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A3FC2-E064-4CF9-A2FD-96B392216D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A10F6B0-884A-4E13-ACAB-78EE3D04BB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22440" yWindow="2265" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="2190" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>(name)</t>
   </si>
@@ -36,21 +36,63 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>고유 ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Description</t>
+    <t>몬스터 데이터 ID</t>
   </si>
   <si>
-    <t>고유 ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>아이템 데이터 ID</t>
+  </si>
+  <si>
+    <t>드랍 확률 (0~1)</t>
+  </si>
+  <si>
+    <t>최소 수량</t>
+  </si>
+  <si>
+    <t>최대 수량</t>
+  </si>
+  <si>
+    <t>MonsterDataId</t>
+  </si>
+  <si>
+    <t>ItemDataId</t>
+  </si>
+  <si>
+    <t>DropChance</t>
+  </si>
+  <si>
+    <t>MinCount</t>
+  </si>
+  <si>
+    <t>MaxCount</t>
+  </si>
+  <si>
+    <t>drop_goblin_attack</t>
+  </si>
+  <si>
+    <t>mob_goblin_1</t>
+  </si>
+  <si>
+    <t>Stat_02</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -71,13 +113,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -90,6 +125,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -97,12 +141,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -128,8 +166,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -152,19 +195,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF222222"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF222222"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF222222"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF222222"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -174,15 +233,25 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{816869D2-9F9B-4672-81B2-2DD417C0E9B9}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -405,347 +474,390 @@
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="50.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
+      <c r="D2" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
+      <c r="B3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="A4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="14">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="E25" s="3"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="E26" s="3"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="E27" s="3"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="E27" s="2"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="E28" s="3"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="E28" s="2"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>
@@ -1713,7 +1825,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>